--- a/Assets/Samples/AdDemo/Excels/Networks/Cmds/NetworkCmds.xlsx
+++ b/Assets/Samples/AdDemo/Excels/Networks/Cmds/NetworkCmds.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13" defaultRowHeight="14.15"/>
   <cols>
     <col width="12" customWidth="1" style="1" min="1" max="1"/>
@@ -722,7 +722,33 @@
       <c r="T5" s="8" t="n"/>
       <c r="U5" s="8" t="n"/>
     </row>
-    <row r="6" ht="22" customHeight="1"/>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>AppCustomConfig</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>拉取GM后台应用配置URL</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>HTTP_POST</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>GameServer</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>/v1/common/app-config</t>
+        </is>
+      </c>
+    </row>
     <row r="7" ht="22" customHeight="1"/>
     <row r="8" ht="22" customHeight="1"/>
     <row r="9" ht="22" customHeight="1"/>

--- a/Assets/Samples/AdDemo/Excels/Networks/Cmds/NetworkCmds.xlsx
+++ b/Assets/Samples/AdDemo/Excels/Networks/Cmds/NetworkCmds.xlsx
@@ -1,57 +1,161 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SoloGames-X\nova\Assets\Samples\AdDemo\Excels\Networks\Cmds\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D0401D-3059-49D3-9DB0-9B4868EF8389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="40749" yWindow="2511" windowWidth="17605" windowHeight="13158" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="NetworkCmds" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="NetworkCmds" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="30">
+  <si>
+    <t>##comment</t>
+  </si>
+  <si>
+    <t>网络指令表（NetCmds）</t>
+  </si>
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>#Desc</t>
+  </si>
+  <si>
+    <t>Way</t>
+  </si>
+  <si>
+    <t>HostKey</t>
+  </si>
+  <si>
+    <t>Path</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>指令唯一名称</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>通信方式</t>
+  </si>
+  <si>
+    <t>主机Key</t>
+  </si>
+  <si>
+    <t>路径</t>
+  </si>
+  <si>
+    <t>TGAServerUrl</t>
+  </si>
+  <si>
+    <t>TGA服务器URL</t>
+  </si>
+  <si>
+    <t>HTTP_URL</t>
+  </si>
+  <si>
+    <t>TGAServer</t>
+  </si>
+  <si>
+    <t>AppCustomConfig</t>
+  </si>
+  <si>
+    <t>拉取GM后台应用配置URL</t>
+  </si>
+  <si>
+    <t>HTTP_POST</t>
+  </si>
+  <si>
+    <t>GameServer</t>
+  </si>
+  <si>
+    <t>/v1/common/app-config</t>
+  </si>
+  <si>
+    <t>AppsFlyerReport</t>
+  </si>
+  <si>
+    <t>Appsflyer 数据上传</t>
+  </si>
+  <si>
+    <t>/v1/user/report-appsflyer</t>
+  </si>
+  <si>
+    <t>FirebaseReport</t>
+  </si>
+  <si>
+    <t>Firebase数据上传</t>
+  </si>
+  <si>
+    <t>/v1/user/report-firebase</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9.75"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
-      <color rgb="FF000000"/>
-      <sz val="9.75"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9.75"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="9.75"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="宋体"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9.75"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="9.75"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -128,104 +232,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -513,281 +558,253 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:U6"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="13" defaultRowHeight="14.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U43"/>
+  <sheetFormatPr defaultColWidth="13" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="12" customWidth="1" style="1" min="1" max="1"/>
-    <col width="37" customWidth="1" style="2" min="2" max="21"/>
-    <col width="13" customWidth="1" style="3" min="22" max="16384"/>
+    <col min="1" max="1" width="12" style="1" customWidth="1"/>
+    <col min="2" max="21" width="37" style="2" customWidth="1"/>
+    <col min="22" max="22" width="13" style="3" customWidth="1"/>
+    <col min="23" max="16384" width="13" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>##comment</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>网络指令表（NetCmds）</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="n"/>
-      <c r="D1" s="4" t="n"/>
-      <c r="E1" s="4" t="n"/>
-      <c r="F1" s="4" t="n"/>
-      <c r="G1" s="4" t="n"/>
-      <c r="H1" s="4" t="n"/>
-      <c r="I1" s="4" t="n"/>
-      <c r="J1" s="4" t="n"/>
-      <c r="K1" s="4" t="n"/>
-      <c r="L1" s="4" t="n"/>
-      <c r="M1" s="4" t="n"/>
-      <c r="N1" s="4" t="n"/>
-      <c r="O1" s="4" t="n"/>
-      <c r="P1" s="4" t="n"/>
-      <c r="Q1" s="4" t="n"/>
-      <c r="R1" s="4" t="n"/>
-      <c r="S1" s="4" t="n"/>
-      <c r="T1" s="4" t="n"/>
-      <c r="U1" s="4" t="n"/>
+    <row r="1" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>#Desc</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>Way</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>HostKey</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>Path</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="n"/>
-      <c r="O2" s="5" t="n"/>
-      <c r="P2" s="5" t="n"/>
-      <c r="Q2" s="5" t="n"/>
-      <c r="R2" s="5" t="n"/>
-      <c r="S2" s="5" t="n"/>
-      <c r="T2" s="5" t="n"/>
-      <c r="U2" s="5" t="n"/>
+    <row r="2" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
     </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
-      <c r="I3" s="6" t="n"/>
-      <c r="J3" s="6" t="n"/>
-      <c r="K3" s="6" t="n"/>
-      <c r="L3" s="6" t="n"/>
-      <c r="M3" s="6" t="n"/>
-      <c r="N3" s="6" t="n"/>
-      <c r="O3" s="6" t="n"/>
-      <c r="P3" s="6" t="n"/>
-      <c r="Q3" s="6" t="n"/>
-      <c r="R3" s="6" t="n"/>
-      <c r="S3" s="6" t="n"/>
-      <c r="T3" s="6" t="n"/>
-      <c r="U3" s="6" t="n"/>
+    <row r="3" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
     </row>
-    <row r="4" ht="22" customFormat="1" customHeight="1" s="1">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>##comment</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>指令唯一名称</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>通信方式</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>主机Key</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>路径</t>
-        </is>
+    <row r="4" spans="1:21" s="1" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>TGAServerUrl</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>TGA服务器URL</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>HTTP_URL</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>TGAServer</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
-      <c r="H5" s="8" t="n"/>
-      <c r="I5" s="8" t="n"/>
-      <c r="J5" s="8" t="n"/>
-      <c r="K5" s="8" t="n"/>
-      <c r="L5" s="8" t="n"/>
-      <c r="M5" s="8" t="n"/>
-      <c r="N5" s="8" t="n"/>
-      <c r="O5" s="8" t="n"/>
-      <c r="P5" s="8" t="n"/>
-      <c r="Q5" s="8" t="n"/>
-      <c r="R5" s="8" t="n"/>
-      <c r="S5" s="8" t="n"/>
-      <c r="T5" s="8" t="n"/>
-      <c r="U5" s="8" t="n"/>
+    <row r="5" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
     </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>AppCustomConfig</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>拉取GM后台应用配置URL</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>HTTP_POST</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>GameServer</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>/v1/common/app-config</t>
-        </is>
+    <row r="6" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1"/>
-    <row r="8" ht="22" customHeight="1"/>
-    <row r="9" ht="22" customHeight="1"/>
-    <row r="10" ht="22" customHeight="1"/>
-    <row r="11" ht="22" customHeight="1"/>
-    <row r="12" ht="22" customHeight="1"/>
-    <row r="13" ht="22" customHeight="1"/>
-    <row r="14" ht="22" customHeight="1"/>
-    <row r="15" ht="22" customHeight="1"/>
-    <row r="16" ht="22" customHeight="1"/>
-    <row r="17" ht="22" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1"/>
-    <row r="19" ht="22" customHeight="1"/>
-    <row r="20" ht="22" customHeight="1"/>
-    <row r="21" ht="22" customHeight="1"/>
-    <row r="22" ht="22" customHeight="1"/>
-    <row r="23" ht="22" customHeight="1"/>
-    <row r="24" ht="22" customHeight="1"/>
-    <row r="25" ht="22" customHeight="1"/>
-    <row r="26" ht="22" customHeight="1"/>
-    <row r="27" ht="22" customHeight="1"/>
-    <row r="28" ht="22" customHeight="1"/>
-    <row r="29" ht="22" customHeight="1"/>
-    <row r="30" ht="22" customHeight="1"/>
-    <row r="31" ht="22" customHeight="1"/>
-    <row r="32" ht="22" customHeight="1"/>
-    <row r="33" ht="22" customHeight="1"/>
-    <row r="34" ht="22" customHeight="1"/>
-    <row r="35" ht="22" customHeight="1"/>
-    <row r="36" ht="22" customHeight="1"/>
-    <row r="37" ht="22" customHeight="1"/>
-    <row r="38" ht="22" customHeight="1"/>
-    <row r="39" ht="22" customHeight="1"/>
-    <row r="40" ht="22" customHeight="1"/>
-    <row r="41" ht="22" customHeight="1"/>
-    <row r="42" ht="22" customHeight="1"/>
-    <row r="43" ht="22" customHeight="1"/>
+    <row r="7" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="22" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>